--- a/data/simulation/simulated_monitoring_data.xlsx
+++ b/data/simulation/simulated_monitoring_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="53">
   <si>
     <t>序号</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>2026-09-07 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -527,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -1290,46 +1293,46 @@
         <v>36</v>
       </c>
       <c r="G11">
-        <v>10.05</v>
+        <v>10.08</v>
       </c>
       <c r="H11">
-        <v>10050</v>
+        <v>10080</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>10.02</v>
+        <v>6.5</v>
       </c>
       <c r="M11">
-        <v>10020</v>
+        <v>6500</v>
       </c>
       <c r="N11">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="O11">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="P11">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="Q11">
-        <v>10.08</v>
+        <v>10.1</v>
       </c>
       <c r="R11">
-        <v>10080</v>
+        <v>10100</v>
       </c>
       <c r="S11">
         <v>120</v>
       </c>
       <c r="T11">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="U11">
         <v>120</v>
@@ -1373,25 +1376,25 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>10.02</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M12">
-        <v>10020</v>
+        <v>8700</v>
       </c>
       <c r="N12">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="O12">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="P12">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="Q12">
         <v>10.08</v>
@@ -1403,7 +1406,7 @@
         <v>120</v>
       </c>
       <c r="T12">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="U12">
         <v>120</v>
@@ -1453,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>5.82</v>
+        <v>10.14</v>
       </c>
       <c r="M13">
-        <v>5820</v>
+        <v>10140</v>
       </c>
       <c r="N13">
         <v>-118</v>
@@ -1521,25 +1524,25 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>10.02</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M14">
-        <v>10020</v>
+        <v>8700</v>
       </c>
       <c r="N14">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="O14">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="P14">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="Q14">
         <v>10.08</v>
@@ -1551,7 +1554,7 @@
         <v>120</v>
       </c>
       <c r="T14">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="U14">
         <v>120</v>
@@ -1595,25 +1598,25 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>10.02</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M15">
-        <v>10020</v>
+        <v>8700</v>
       </c>
       <c r="N15">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="O15">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="P15">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="Q15">
         <v>10.08</v>
@@ -1625,7 +1628,7 @@
         <v>120</v>
       </c>
       <c r="T15">
-        <v>0.1</v>
+        <v>12</v>
       </c>
       <c r="U15">
         <v>120</v>
@@ -3118,6 +3121,524 @@
       </c>
       <c r="X35" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36">
+        <v>10.1</v>
+      </c>
+      <c r="H36">
+        <v>10100</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>15</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>10.08</v>
+      </c>
+      <c r="M36">
+        <v>10080</v>
+      </c>
+      <c r="N36">
+        <v>-120</v>
+      </c>
+      <c r="O36">
+        <v>15</v>
+      </c>
+      <c r="P36">
+        <v>-120</v>
+      </c>
+      <c r="Q36">
+        <v>10.15</v>
+      </c>
+      <c r="R36">
+        <v>10150</v>
+      </c>
+      <c r="S36">
+        <v>120</v>
+      </c>
+      <c r="T36">
+        <v>15</v>
+      </c>
+      <c r="U36">
+        <v>120</v>
+      </c>
+      <c r="V36">
+        <v>23.5</v>
+      </c>
+      <c r="W36">
+        <v>65</v>
+      </c>
+      <c r="X36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37">
+        <v>2.5</v>
+      </c>
+      <c r="H37">
+        <v>2500</v>
+      </c>
+      <c r="I37">
+        <v>40</v>
+      </c>
+      <c r="J37">
+        <v>350</v>
+      </c>
+      <c r="K37">
+        <v>40</v>
+      </c>
+      <c r="L37">
+        <v>10.15</v>
+      </c>
+      <c r="M37">
+        <v>10150</v>
+      </c>
+      <c r="N37">
+        <v>-120</v>
+      </c>
+      <c r="O37">
+        <v>30</v>
+      </c>
+      <c r="P37">
+        <v>-120</v>
+      </c>
+      <c r="Q37">
+        <v>10.2</v>
+      </c>
+      <c r="R37">
+        <v>10200</v>
+      </c>
+      <c r="S37">
+        <v>120</v>
+      </c>
+      <c r="T37">
+        <v>30</v>
+      </c>
+      <c r="U37">
+        <v>120</v>
+      </c>
+      <c r="V37">
+        <v>23.5</v>
+      </c>
+      <c r="W37">
+        <v>65</v>
+      </c>
+      <c r="X37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38">
+        <v>7.5</v>
+      </c>
+      <c r="H38">
+        <v>7500</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>25</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>10.05</v>
+      </c>
+      <c r="M38">
+        <v>10050</v>
+      </c>
+      <c r="N38">
+        <v>-120</v>
+      </c>
+      <c r="O38">
+        <v>25</v>
+      </c>
+      <c r="P38">
+        <v>-120</v>
+      </c>
+      <c r="Q38">
+        <v>10.1</v>
+      </c>
+      <c r="R38">
+        <v>10100</v>
+      </c>
+      <c r="S38">
+        <v>120</v>
+      </c>
+      <c r="T38">
+        <v>25</v>
+      </c>
+      <c r="U38">
+        <v>120</v>
+      </c>
+      <c r="V38">
+        <v>23.5</v>
+      </c>
+      <c r="W38">
+        <v>65</v>
+      </c>
+      <c r="X38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>10.1</v>
+      </c>
+      <c r="H39">
+        <v>10100</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>15</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>10.08</v>
+      </c>
+      <c r="M39">
+        <v>10080</v>
+      </c>
+      <c r="N39">
+        <v>-120</v>
+      </c>
+      <c r="O39">
+        <v>15</v>
+      </c>
+      <c r="P39">
+        <v>-120</v>
+      </c>
+      <c r="Q39">
+        <v>10.15</v>
+      </c>
+      <c r="R39">
+        <v>10150</v>
+      </c>
+      <c r="S39">
+        <v>120</v>
+      </c>
+      <c r="T39">
+        <v>15</v>
+      </c>
+      <c r="U39">
+        <v>120</v>
+      </c>
+      <c r="V39">
+        <v>23.5</v>
+      </c>
+      <c r="W39">
+        <v>65</v>
+      </c>
+      <c r="X39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40">
+        <v>10.1</v>
+      </c>
+      <c r="H40">
+        <v>10100</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>15</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>10.08</v>
+      </c>
+      <c r="M40">
+        <v>10080</v>
+      </c>
+      <c r="N40">
+        <v>-120</v>
+      </c>
+      <c r="O40">
+        <v>15</v>
+      </c>
+      <c r="P40">
+        <v>-120</v>
+      </c>
+      <c r="Q40">
+        <v>10.15</v>
+      </c>
+      <c r="R40">
+        <v>10150</v>
+      </c>
+      <c r="S40">
+        <v>120</v>
+      </c>
+      <c r="T40">
+        <v>15</v>
+      </c>
+      <c r="U40">
+        <v>120</v>
+      </c>
+      <c r="V40">
+        <v>23.5</v>
+      </c>
+      <c r="W40">
+        <v>65</v>
+      </c>
+      <c r="X40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41">
+        <v>10.1</v>
+      </c>
+      <c r="H41">
+        <v>10100</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>10.08</v>
+      </c>
+      <c r="M41">
+        <v>10080</v>
+      </c>
+      <c r="N41">
+        <v>-120</v>
+      </c>
+      <c r="O41">
+        <v>15</v>
+      </c>
+      <c r="P41">
+        <v>-120</v>
+      </c>
+      <c r="Q41">
+        <v>10.15</v>
+      </c>
+      <c r="R41">
+        <v>10150</v>
+      </c>
+      <c r="S41">
+        <v>120</v>
+      </c>
+      <c r="T41">
+        <v>15</v>
+      </c>
+      <c r="U41">
+        <v>120</v>
+      </c>
+      <c r="V41">
+        <v>23.5</v>
+      </c>
+      <c r="W41">
+        <v>65</v>
+      </c>
+      <c r="X41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42">
+        <v>10.1</v>
+      </c>
+      <c r="H42">
+        <v>10100</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>15</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>10.08</v>
+      </c>
+      <c r="M42">
+        <v>10080</v>
+      </c>
+      <c r="N42">
+        <v>-120</v>
+      </c>
+      <c r="O42">
+        <v>15</v>
+      </c>
+      <c r="P42">
+        <v>-120</v>
+      </c>
+      <c r="Q42">
+        <v>10.15</v>
+      </c>
+      <c r="R42">
+        <v>10150</v>
+      </c>
+      <c r="S42">
+        <v>120</v>
+      </c>
+      <c r="T42">
+        <v>15</v>
+      </c>
+      <c r="U42">
+        <v>120</v>
+      </c>
+      <c r="V42">
+        <v>23.5</v>
+      </c>
+      <c r="W42">
+        <v>65</v>
+      </c>
+      <c r="X42" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
